--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6493-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6493-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{475E19F5-1287-4452-8168-49A227FB7829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20659622-0404-4A43-A9FA-60BA50B3778E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{AEF14BDA-7F9D-423E-9888-060FA43CDAAA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{48E971BE-01D6-4F28-AA98-5B8B8306C0DD}"/>
   </bookViews>
   <sheets>
     <sheet name="6493-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1460,20 +1460,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED30B1D2-6C2D-4C8D-AF1A-F4F8BEB195A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9C8D0E-59FB-469C-8284-4B38865F5D0C}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1627,7 +1627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2025</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2023</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2021</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>26</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>26</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>26</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2020</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2019</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2018</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2017</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2016</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2015</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
         <v>39</v>
       </c>
